--- a/data/gebze/km_data.xlsx
+++ b/data/gebze/km_data.xlsx
@@ -450,11 +450,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-06 01:02:52</t>
+          <t>2026-04-06 10:36:43</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -470,11 +470,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-06 01:02:52</t>
+          <t>2026-04-06 10:36:43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -490,11 +490,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-06 01:02:53</t>
+          <t>2026-04-06 10:36:43</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -510,11 +510,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-06 01:02:53</t>
+          <t>2026-04-06 10:36:43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -530,11 +530,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62000</v>
+        <v>10000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-06 01:02:53</t>
+          <t>2026-04-06 10:36:43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -550,11 +550,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-06 01:02:53</t>
+          <t>2026-04-06 10:36:43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -570,12 +570,12 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>95000</v>
+        <v>10000</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-06 01:02:54</t>
+          <t>2026-04-06 10:36:44</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
